--- a/dev/ValueSet-mii-vs-pro-ssd-12-answers.xlsx
+++ b/dev/ValueSet-mii-vs-pro-ssd-12-answers.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.6.0</t>
+    <t>2026.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:53+00:00</t>
+    <t>2026-09-02T06:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-ssd-12-answers.xlsx
+++ b/dev/ValueSet-mii-vs-pro-ssd-12-answers.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:55+00:00</t>
+    <t>2026-09-02T06:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-ssd-12-answers.xlsx
+++ b/dev/ValueSet-mii-vs-pro-ssd-12-answers.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:47:03+00:00</t>
+    <t>2026-09-02T07:20:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
